--- a/data-raw/Data.xlsx
+++ b/data-raw/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="0" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="8" state="visible" r:id="rId3"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="629">
   <si>
     <t>date</t>
   </si>
@@ -1835,6 +1835,78 @@
   <si>
     <t xml:space="preserve">Annual end-June (chain volume), placed on the June quarter; blank elsewhere. Interpolation and identities done in calculate_estimation_data.R.; beyond the last published benchmark the final quarterly increment continues (no new 5204.0 benchmark in the current release)</t>
   </si>
+  <si>
+    <t xml:space="preserve">ABS 5206.0, Table 20 household income (A2302887W)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABS 5206.0, Table 20 household income (A2302889A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABS 5206.0, Table 20 household income (A2302902J)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASX All Ordinaries index via Yahoo Finance chart API (^AORD, end-of-quarter close); the old FRED SPASTT01AUQ661N was a rebased OECD index (removed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End-of-quarter close, index points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABS 5232.0 Table 1 (other private non-financial corporations + private non-financial investment funds, loans and placements, $m / 1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABS 5232.0 Table 1 (other private non-financial corporations + private non-financial investment funds, bonds, $m / 1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABS 5232.0 Table 1 (other private non-financial corporations + private non-financial investment funds, shares and other equity, $m / 1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived: KBiz - KMin (validated exact over 199 quarters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterly; equals KBiz less KMin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived: KTotal - KBiz - KDwell (validated exact over 199 quarters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterly; residual stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATO statutory company income tax rate (0.49 to 0.30, constant since 2001-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterly; statutory constant, held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital-stock calibration (non-mining depreciation rate, calibrated level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterly; calibrated constant, held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario model correction series (COVID transfers correction; zero after 2022Q1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterly; zero after the correction period, held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSEG / Refinitiv ASX All Ordinaries calculated P/E (subscription; no free endpoint found - Yahoo/FRED/Stooq checked)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSEG / Refinitiv ASX 200 earnings (subscription; no free endpoint found)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABS 6291.0.55.001 detailed labour force, market-sector aggregate via Temp/Masterdata.xlsx; the workbook's own labour-account series reproduce it only to ~4.7% - the industry-table derivation is needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6224.0.55.001 annual households, interpolated quarterly; the series ceased - the June 2025 experimental estimate (10.9m) extends it to 2025Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom quarterly derivation from the annual fiscal balance (ABS GFS checked: the quarterly net-lending series does not reproduce it; the derivation is needed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public-sector net debt from annual fiscal data (ABS GFS annual net debt checked: 846.6b 2023-24, 954.9b 2024-25; the workbook's quarterly path is a custom interpolation - the derivation is needed)</t>
+  </si>
 </sst>
 </file>
 
@@ -2237,7 +2309,7 @@
         <v>60</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>626</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>62</v>
@@ -3144,7 +3216,9 @@
         <v>307</v>
       </c>
       <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
+      <c r="C68" s="2" t="s">
+        <v>610</v>
+      </c>
       <c r="D68" s="2" t="s">
         <v>71</v>
       </c>
@@ -3154,7 +3228,9 @@
         <v>308</v>
       </c>
       <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
+      <c r="C69" s="2" t="s">
+        <v>611</v>
+      </c>
       <c r="D69" s="2" t="s">
         <v>71</v>
       </c>
@@ -3164,7 +3240,9 @@
         <v>321</v>
       </c>
       <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
+      <c r="C70" s="2" t="s">
+        <v>605</v>
+      </c>
       <c r="D70" s="2" t="s">
         <v>71</v>
       </c>
@@ -3174,7 +3252,9 @@
         <v>322</v>
       </c>
       <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
+      <c r="C71" s="2" t="s">
+        <v>606</v>
+      </c>
       <c r="D71" s="2" t="s">
         <v>71</v>
       </c>
@@ -3184,7 +3264,9 @@
         <v>323</v>
       </c>
       <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
+      <c r="C72" s="2" t="s">
+        <v>607</v>
+      </c>
       <c r="D72" s="2" t="s">
         <v>71</v>
       </c>
@@ -3469,7 +3551,7 @@
         <v>215</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>216</v>
+        <v>623</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>217</v>
@@ -3483,7 +3565,7 @@
         <v>218</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>219</v>
+        <v>624</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>71</v>
@@ -3665,7 +3747,7 @@
         <v>460</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>461</v>
+        <v>627</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>244</v>
@@ -3679,7 +3761,7 @@
         <v>462</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>463</v>
+        <v>628</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>220</v>
@@ -3704,7 +3786,9 @@
         <v>309</v>
       </c>
       <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
+      <c r="C111" s="2" t="s">
+        <v>612</v>
+      </c>
       <c r="D111" s="2" t="s">
         <v>71</v>
       </c>
@@ -3717,10 +3801,10 @@
         <v>224</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>225</v>
+        <v>617</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>226</v>
+        <v>618</v>
       </c>
     </row>
     <row r="113">
@@ -3731,10 +3815,10 @@
         <v>464</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>465</v>
+        <v>619</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>227</v>
+        <v>620</v>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1">
@@ -3745,10 +3829,10 @@
         <v>228</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>229</v>
+        <v>621</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>230</v>
+        <v>622</v>
       </c>
     </row>
     <row r="115" ht="60" customHeight="1">
@@ -3756,9 +3840,11 @@
         <v>382</v>
       </c>
       <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
+      <c r="C115" s="2" t="s">
+        <v>608</v>
+      </c>
       <c r="D115" s="2" t="s">
-        <v>395</v>
+        <v>609</v>
       </c>
     </row>
     <row r="116" ht="105" customHeight="1">
@@ -3769,7 +3855,7 @@
         <v>231</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>232</v>
+        <v>625</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>396</v>
@@ -3848,8 +3934,12 @@
         <v>398</v>
       </c>
       <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
+      <c r="C122" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>614</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
@@ -3859,9 +3949,11 @@
         <v>468</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D123" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="2" t="s">
@@ -7029,10 +7121,10 @@
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>477273.358202773</v>
+        <v>477273.358202774</v>
       </c>
       <c r="DS6" t="n">
-        <v>614736.488103409</v>
+        <v>614736.488103411</v>
       </c>
     </row>
     <row r="7">
@@ -7315,7 +7407,7 @@
         <v>481120.478628794</v>
       </c>
       <c r="DS7" t="n">
-        <v>619865.414263451</v>
+        <v>619865.414263452</v>
       </c>
     </row>
     <row r="8">
@@ -7597,10 +7689,10 @@
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>484998.609240735</v>
+        <v>484998.609240734</v>
       </c>
       <c r="DS8" t="n">
-        <v>625037.132553233</v>
+        <v>625037.132553235</v>
       </c>
     </row>
     <row r="9">
@@ -8172,7 +8264,7 @@
         <v>493143.638430756</v>
       </c>
       <c r="DS10" t="n">
-        <v>634595.639378127</v>
+        <v>634595.639378131</v>
       </c>
     </row>
     <row r="11">
@@ -8456,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>497415.972176206</v>
+        <v>497415.972176207</v>
       </c>
       <c r="DS11" t="n">
-        <v>638969.214723213</v>
+        <v>638969.214723208</v>
       </c>
     </row>
     <row r="12">
@@ -8746,7 +8838,7 @@
         <v>501725.319145005</v>
       </c>
       <c r="DS12" t="n">
-        <v>643372.932351214</v>
+        <v>643372.932351213</v>
       </c>
     </row>
     <row r="13">
@@ -9035,7 +9127,7 @@
         <v>506072</v>
       </c>
       <c r="DS13" t="n">
-        <v>647806.999999999</v>
+        <v>647807</v>
       </c>
     </row>
     <row r="14">
@@ -9324,7 +9416,7 @@
         <v>510452.787899665</v>
       </c>
       <c r="DS14" t="n">
-        <v>651753.784415121</v>
+        <v>651753.784415119</v>
       </c>
     </row>
     <row r="15">
@@ -9613,7 +9705,7 @@
         <v>514871.49787884</v>
       </c>
       <c r="DS15" t="n">
-        <v>655724.614737772</v>
+        <v>655724.614737776</v>
       </c>
     </row>
     <row r="16">
@@ -9912,7 +10004,7 @@
         <v>519328.45820818</v>
       </c>
       <c r="DS16" t="n">
-        <v>659719.637468397</v>
+        <v>659719.637468401</v>
       </c>
     </row>
     <row r="17">
@@ -10510,7 +10602,7 @@
         <v>529344.36985434</v>
       </c>
       <c r="DS18" t="n">
-        <v>669148.264292408</v>
+        <v>669148.264292404</v>
       </c>
     </row>
     <row r="19">
@@ -10809,7 +10901,7 @@
         <v>534922.916659961</v>
       </c>
       <c r="DS19" t="n">
-        <v>674601.61238912</v>
+        <v>674601.612389116</v>
       </c>
     </row>
     <row r="20">
@@ -11108,7 +11200,7 @@
         <v>540560.253520289</v>
       </c>
       <c r="DS20" t="n">
-        <v>680099.40355929</v>
+        <v>680099.403559288</v>
       </c>
     </row>
     <row r="21">
@@ -11706,7 +11798,7 @@
         <v>551237.227954169</v>
       </c>
       <c r="DS22" t="n">
-        <v>690086.595558803</v>
+        <v>690086.595558808</v>
       </c>
     </row>
     <row r="23">
@@ -12009,7 +12101,7 @@
         <v>556262.860672902</v>
       </c>
       <c r="DS23" t="n">
-        <v>694560.002698112</v>
+        <v>694560.002698108</v>
       </c>
     </row>
     <row r="24">
@@ -12312,7 +12404,7 @@
         <v>561334.312111674</v>
       </c>
       <c r="DS24" t="n">
-        <v>699062.408185689</v>
+        <v>699062.408185687</v>
       </c>
     </row>
     <row r="25">
@@ -12918,7 +13010,7 @@
         <v>572905.62022307</v>
       </c>
       <c r="DS26" t="n">
-        <v>708049.990084786</v>
+        <v>708049.990084788</v>
       </c>
     </row>
     <row r="27">
@@ -13221,7 +13313,7 @@
         <v>579432.766912607</v>
       </c>
       <c r="DS27" t="n">
-        <v>712534.200773549</v>
+        <v>712534.200773548</v>
       </c>
     </row>
     <row r="28">
@@ -13524,7 +13616,7 @@
         <v>586034.277759876</v>
       </c>
       <c r="DS28" t="n">
-        <v>717046.810792562</v>
+        <v>717046.810792565</v>
       </c>
     </row>
     <row r="29">
@@ -13828,7 +13920,7 @@
         <v>0</v>
       </c>
       <c r="DR29" t="n">
-        <v>592711</v>
+        <v>592711.000000001</v>
       </c>
       <c r="DS29" t="n">
         <v>721588</v>
@@ -14138,7 +14230,7 @@
         <v>600264.622072927</v>
       </c>
       <c r="DS30" t="n">
-        <v>725805.873785546</v>
+        <v>725805.873785545</v>
       </c>
     </row>
     <row r="31">
@@ -14445,7 +14537,7 @@
         <v>607914.508946776</v>
       </c>
       <c r="DS31" t="n">
-        <v>730048.402165226</v>
+        <v>730048.402165224</v>
       </c>
     </row>
     <row r="32">
@@ -14749,10 +14841,10 @@
         <v>0</v>
       </c>
       <c r="DR32" t="n">
-        <v>615661.887438541</v>
+        <v>615661.88743854</v>
       </c>
       <c r="DS32" t="n">
-        <v>734315.729251699</v>
+        <v>734315.729251697</v>
       </c>
     </row>
     <row r="33">
@@ -15059,7 +15151,7 @@
         <v>623508</v>
       </c>
       <c r="DS33" t="n">
-        <v>738607.999999999</v>
+        <v>738608</v>
       </c>
     </row>
     <row r="34">
@@ -15363,10 +15455,10 @@
         <v>0</v>
       </c>
       <c r="DR34" t="n">
-        <v>628823.148753308</v>
+        <v>628823.148753307</v>
       </c>
       <c r="DS34" t="n">
-        <v>741487.863118156</v>
+        <v>741487.863118166</v>
       </c>
     </row>
     <row r="35">
@@ -15673,7 +15765,7 @@
         <v>634183.606959372</v>
       </c>
       <c r="DS35" t="n">
-        <v>744378.954941635</v>
+        <v>744378.95494163</v>
       </c>
     </row>
     <row r="36">
@@ -15977,10 +16069,10 @@
         <v>0</v>
       </c>
       <c r="DR36" t="n">
-        <v>639589.760862608</v>
+        <v>639589.760862609</v>
       </c>
       <c r="DS36" t="n">
-        <v>747281.319251618</v>
+        <v>747281.319251614</v>
       </c>
     </row>
     <row r="37">
@@ -16594,7 +16686,7 @@
         <v>650989.000292926</v>
       </c>
       <c r="DS38" t="n">
-        <v>754463.923627897</v>
+        <v>754463.923627894</v>
       </c>
     </row>
     <row r="39">
@@ -16898,10 +16990,10 @@
         <v>0</v>
       </c>
       <c r="DR39" t="n">
-        <v>656990.829283027</v>
+        <v>656990.829283026</v>
       </c>
       <c r="DS39" t="n">
-        <v>758757.139218472</v>
+        <v>758757.139218469</v>
       </c>
     </row>
     <row r="40">
@@ -17205,10 +17297,10 @@
         <v>0</v>
       </c>
       <c r="DR40" t="n">
-        <v>663047.992466503</v>
+        <v>663047.992466502</v>
       </c>
       <c r="DS40" t="n">
-        <v>763074.785003162</v>
+        <v>763074.785003166</v>
       </c>
     </row>
     <row r="41">
@@ -17822,7 +17914,7 @@
         <v>675545.30090397</v>
       </c>
       <c r="DS42" t="n">
-        <v>773532.753675872</v>
+        <v>773532.753675873</v>
       </c>
     </row>
     <row r="43">
@@ -18134,10 +18226,10 @@
         <v>0</v>
       </c>
       <c r="DR43" t="n">
-        <v>681990.512856301</v>
+        <v>681990.512856302</v>
       </c>
       <c r="DS43" t="n">
-        <v>779697.245447232</v>
+        <v>779697.245447228</v>
       </c>
     </row>
     <row r="44">
@@ -18452,7 +18544,7 @@
         <v>688497.216994359</v>
       </c>
       <c r="DS44" t="n">
-        <v>785910.863721144</v>
+        <v>785910.863721141</v>
       </c>
     </row>
     <row r="45">
@@ -19090,7 +19182,7 @@
         <v>702556.058153322</v>
       </c>
       <c r="DS46" t="n">
-        <v>798514.226307259</v>
+        <v>798514.226307258</v>
       </c>
     </row>
     <row r="47">
@@ -19411,7 +19503,7 @@
         <v>710126.829463583</v>
       </c>
       <c r="DS47" t="n">
-        <v>804905.197109573</v>
+        <v>804905.197109567</v>
       </c>
     </row>
     <row r="48">
@@ -19732,7 +19824,7 @@
         <v>717779.183698888</v>
       </c>
       <c r="DS48" t="n">
-        <v>811347.318544463</v>
+        <v>811347.318544459</v>
       </c>
     </row>
     <row r="49">
@@ -20053,7 +20145,7 @@
         <v>725514</v>
       </c>
       <c r="DS49" t="n">
-        <v>817841.000000001</v>
+        <v>817841</v>
       </c>
     </row>
     <row r="50">
@@ -20378,7 +20470,7 @@
         <v>733087.824844783</v>
       </c>
       <c r="DS50" t="n">
-        <v>824324.7383161</v>
+        <v>824324.738316096</v>
       </c>
     </row>
     <row r="51">
@@ -20703,7 +20795,7 @@
         <v>740740.714770019</v>
       </c>
       <c r="DS51" t="n">
-        <v>830859.878876095</v>
+        <v>830859.878876097</v>
       </c>
     </row>
     <row r="52">
@@ -21353,7 +21445,7 @@
         <v>756287</v>
       </c>
       <c r="DS53" t="n">
-        <v>844086.000000001</v>
+        <v>844086</v>
       </c>
     </row>
     <row r="54">
@@ -21680,7 +21772,7 @@
         <v>764145.659008284</v>
       </c>
       <c r="DS54" t="n">
-        <v>851995.383336997</v>
+        <v>851995.383337002</v>
       </c>
     </row>
     <row r="55">
@@ -22007,7 +22099,7 @@
         <v>772085.978181835</v>
       </c>
       <c r="DS55" t="n">
-        <v>859978.8803837</v>
+        <v>859978.880383694</v>
       </c>
     </row>
     <row r="56">
@@ -22334,7 +22426,7 @@
         <v>780108.806060151</v>
       </c>
       <c r="DS56" t="n">
-        <v>868037.185611691</v>
+        <v>868037.185611694</v>
       </c>
     </row>
     <row r="57">
@@ -22664,7 +22756,7 @@
         <v>0</v>
       </c>
       <c r="DR57" t="n">
-        <v>788214.999999999</v>
+        <v>788215</v>
       </c>
       <c r="DS57" t="n">
         <v>876171</v>
@@ -23004,7 +23096,7 @@
         <v>796027.090897519</v>
       </c>
       <c r="DS58" t="n">
-        <v>886133.297424569</v>
+        <v>886133.29742457</v>
       </c>
     </row>
     <row r="59">
@@ -23338,10 +23430,10 @@
         <v>0</v>
       </c>
       <c r="DR59" t="n">
-        <v>803916.608340069</v>
+        <v>803916.608340072</v>
       </c>
       <c r="DS59" t="n">
-        <v>896208.868821883</v>
+        <v>896208.86882188</v>
       </c>
     </row>
     <row r="60">
@@ -23675,10 +23767,10 @@
         <v>0</v>
       </c>
       <c r="DR60" t="n">
-        <v>811884.319711177</v>
+        <v>811884.319711181</v>
       </c>
       <c r="DS60" t="n">
-        <v>906399.002147158</v>
+        <v>906399.00214716</v>
       </c>
     </row>
     <row r="61">
@@ -24349,10 +24441,10 @@
         <v>0</v>
       </c>
       <c r="DR62" t="n">
-        <v>827883.551780728</v>
+        <v>827883.55178073</v>
       </c>
       <c r="DS62" t="n">
-        <v>925353.829749021</v>
+        <v>925353.82974902</v>
       </c>
     </row>
     <row r="63">
@@ -24686,10 +24778,10 @@
         <v>0</v>
       </c>
       <c r="DR63" t="n">
-        <v>835913.235758951</v>
+        <v>835913.235758954</v>
       </c>
       <c r="DS63" t="n">
-        <v>934084.258546839</v>
+        <v>934084.25854684</v>
       </c>
     </row>
     <row r="64">
@@ -25026,7 +25118,7 @@
         <v>844020.800043712</v>
       </c>
       <c r="DS64" t="n">
-        <v>942897.056255386</v>
+        <v>942897.05625539</v>
       </c>
     </row>
     <row r="65">
@@ -25697,10 +25789,10 @@
         <v>0</v>
       </c>
       <c r="DR66" t="n">
-        <v>857929.845358294</v>
+        <v>857929.845358291</v>
       </c>
       <c r="DS66" t="n">
-        <v>955730.992666611</v>
+        <v>955730.99266661</v>
       </c>
     </row>
     <row r="67">
@@ -26034,10 +26126,10 @@
         <v>0</v>
       </c>
       <c r="DR67" t="n">
-        <v>863691.121472254</v>
+        <v>863691.121472256</v>
       </c>
       <c r="DS67" t="n">
-        <v>959685.278567406</v>
+        <v>959685.2785674</v>
       </c>
     </row>
     <row r="68">
@@ -26371,7 +26463,7 @@
         <v>0</v>
       </c>
       <c r="DR68" t="n">
-        <v>869491.086416824</v>
+        <v>869491.086416823</v>
       </c>
       <c r="DS68" t="n">
         <v>963655.92511477</v>
@@ -26711,7 +26803,7 @@
         <v>875330</v>
       </c>
       <c r="DS69" t="n">
-        <v>967643.000000001</v>
+        <v>967643</v>
       </c>
     </row>
     <row r="70">
@@ -27045,10 +27137,10 @@
         <v>0</v>
       </c>
       <c r="DR70" t="n">
-        <v>879409.147305774</v>
+        <v>879409.147305771</v>
       </c>
       <c r="DS70" t="n">
-        <v>969196.007276912</v>
+        <v>969196.00727692</v>
       </c>
     </row>
     <row r="71">
@@ -27382,10 +27474,10 @@
         <v>0</v>
       </c>
       <c r="DR71" t="n">
-        <v>883507.303948303</v>
+        <v>883507.3039483</v>
       </c>
       <c r="DS71" t="n">
-        <v>970751.507034628</v>
+        <v>970751.50703463</v>
       </c>
     </row>
     <row r="72">
@@ -27719,10 +27811,10 @@
         <v>0</v>
       </c>
       <c r="DR72" t="n">
-        <v>887624.558513476</v>
+        <v>887624.55851348</v>
       </c>
       <c r="DS72" t="n">
-        <v>972309.503273424</v>
+        <v>972309.50327342</v>
       </c>
     </row>
     <row r="73">
@@ -28393,10 +28485,10 @@
         <v>0</v>
       </c>
       <c r="DR74" t="n">
-        <v>895768.406187756</v>
+        <v>895768.40618776</v>
       </c>
       <c r="DS74" t="n">
-        <v>974353.639605821</v>
+        <v>974353.639605819</v>
       </c>
     </row>
     <row r="75">
@@ -28730,7 +28822,7 @@
         <v>0</v>
       </c>
       <c r="DR75" t="n">
-        <v>899793.8209051</v>
+        <v>899793.820905105</v>
       </c>
       <c r="DS75" t="n">
         <v>974837.5193949</v>
@@ -29067,10 +29159,10 @@
         <v>0</v>
       </c>
       <c r="DR76" t="n">
-        <v>903837.325078977</v>
+        <v>903837.325078973</v>
       </c>
       <c r="DS76" t="n">
-        <v>975321.639486513</v>
+        <v>975321.63948652</v>
       </c>
     </row>
     <row r="77">
@@ -29741,10 +29833,10 @@
         <v>0</v>
       </c>
       <c r="DR78" t="n">
-        <v>911991.742064695</v>
+        <v>911991.742064698</v>
       </c>
       <c r="DS78" t="n">
-        <v>976608.509473257</v>
+        <v>976608.50947326</v>
       </c>
     </row>
     <row r="79">
@@ -30080,10 +30172,10 @@
         <v>0</v>
       </c>
       <c r="DR79" t="n">
-        <v>916102.933910268</v>
+        <v>916102.933910264</v>
       </c>
       <c r="DS79" t="n">
-        <v>977411.678935748</v>
+        <v>977411.67893575</v>
       </c>
     </row>
     <row r="80">
@@ -30419,10 +30511,10 @@
         <v>0</v>
       </c>
       <c r="DR80" t="n">
-        <v>920232.658706974</v>
+        <v>920232.658706977</v>
       </c>
       <c r="DS80" t="n">
-        <v>978215.508930254</v>
+        <v>978215.50893025</v>
       </c>
     </row>
     <row r="81">
@@ -30761,7 +30853,7 @@
         <v>924381</v>
       </c>
       <c r="DS81" t="n">
-        <v>979019.999999999</v>
+        <v>979020</v>
       </c>
     </row>
     <row r="82">
@@ -31105,10 +31197,10 @@
         <v>0</v>
       </c>
       <c r="DR82" t="n">
-        <v>931556.272490614</v>
+        <v>931556.272490618</v>
       </c>
       <c r="DS82" t="n">
-        <v>981051.915508058</v>
+        <v>981051.91550806</v>
       </c>
     </row>
     <row r="83">
@@ -31452,10 +31544,10 @@
         <v>0</v>
       </c>
       <c r="DR83" t="n">
-        <v>938787.241209636</v>
+        <v>938787.241209641</v>
       </c>
       <c r="DS83" t="n">
-        <v>983088.048172696</v>
+        <v>983088.04817269</v>
       </c>
     </row>
     <row r="84">
@@ -31799,10 +31891,10 @@
         <v>0</v>
       </c>
       <c r="DR84" t="n">
-        <v>946074.338484882</v>
+        <v>946074.338484884</v>
       </c>
       <c r="DS84" t="n">
-        <v>985128.406746442</v>
+        <v>985128.40674644</v>
       </c>
     </row>
     <row r="85">
@@ -32493,10 +32585,10 @@
         <v>0</v>
       </c>
       <c r="DR86" t="n">
-        <v>961798.84556955</v>
+        <v>961798.845569547</v>
       </c>
       <c r="DS86" t="n">
-        <v>990234.726563686</v>
+        <v>990234.72656369</v>
       </c>
     </row>
     <row r="87">
@@ -32840,10 +32932,10 @@
         <v>0</v>
       </c>
       <c r="DR87" t="n">
-        <v>970253.361420613</v>
+        <v>970253.361420615</v>
       </c>
       <c r="DS87" t="n">
-        <v>993305.949101787</v>
+        <v>993305.949101789</v>
       </c>
     </row>
     <row r="88">
@@ -33187,10 +33279,10 @@
         <v>0</v>
       </c>
       <c r="DR88" t="n">
-        <v>978782.19513825</v>
+        <v>978782.195138246</v>
       </c>
       <c r="DS88" t="n">
-        <v>996386.697066156</v>
+        <v>996386.69706616</v>
       </c>
     </row>
     <row r="89">
@@ -33534,7 +33626,7 @@
         <v>0</v>
       </c>
       <c r="DR89" t="n">
-        <v>987385.999999999</v>
+        <v>987386</v>
       </c>
       <c r="DS89" t="n">
         <v>999477</v>
@@ -33883,7 +33975,7 @@
         <v>0</v>
       </c>
       <c r="DR90" t="n">
-        <v>996068.795973186</v>
+        <v>996068.795973183</v>
       </c>
       <c r="DS90" t="n">
         <v>1004770.79293158</v>
@@ -35628,7 +35720,7 @@
         <v>0</v>
       </c>
       <c r="DR95" t="n">
-        <v>1040489.13722922</v>
+        <v>1040489.13722921</v>
       </c>
       <c r="DS95" t="n">
         <v>1030517.94358323</v>
@@ -35980,7 +36072,7 @@
         <v>1049562.01171369</v>
       </c>
       <c r="DS96" t="n">
-        <v>1035400.90319414</v>
+        <v>1035400.90319413</v>
       </c>
     </row>
     <row r="97">
@@ -37373,10 +37465,10 @@
         <v>0</v>
       </c>
       <c r="DR100" t="n">
-        <v>1087151.94041417</v>
+        <v>1087151.94041416</v>
       </c>
       <c r="DS100" t="n">
-        <v>1056589.91998705</v>
+        <v>1056589.91998706</v>
       </c>
     </row>
     <row r="101">
@@ -38071,7 +38163,7 @@
         <v>0</v>
       </c>
       <c r="DR102" t="n">
-        <v>1108368.19132145</v>
+        <v>1108368.19132146</v>
       </c>
       <c r="DS102" t="n">
         <v>1068917.32443124</v>
@@ -38420,7 +38512,7 @@
         <v>0</v>
       </c>
       <c r="DR103" t="n">
-        <v>1120058.39490627</v>
+        <v>1120058.39490626</v>
       </c>
       <c r="DS103" t="n">
         <v>1075804.7428609</v>
@@ -38769,7 +38861,7 @@
         <v>0</v>
       </c>
       <c r="DR104" t="n">
-        <v>1131871.89764467</v>
+        <v>1131871.89764466</v>
       </c>
       <c r="DS104" t="n">
         <v>1082736.53940244</v>
@@ -39474,7 +39566,7 @@
         <v>1152031.67860685</v>
       </c>
       <c r="DS106" t="n">
-        <v>1096157.84943228</v>
+        <v>1096157.84943227</v>
       </c>
     </row>
     <row r="107">
@@ -39827,7 +39919,7 @@
         <v>1160312.45444062</v>
       </c>
       <c r="DS107" t="n">
-        <v>1102640.81540001</v>
+        <v>1102640.8154</v>
       </c>
     </row>
     <row r="108">
@@ -40180,7 +40272,7 @@
         <v>1168652.75229073</v>
       </c>
       <c r="DS108" t="n">
-        <v>1109162.12333443</v>
+        <v>1109162.12333442</v>
       </c>
     </row>
     <row r="109">
@@ -42321,10 +42413,10 @@
         <v>0</v>
       </c>
       <c r="DR114" t="n">
-        <v>1224331.46162843</v>
+        <v>1224331.46162842</v>
       </c>
       <c r="DS114" t="n">
-        <v>1149288.90611842</v>
+        <v>1149288.90611843</v>
       </c>
     </row>
     <row r="115">
@@ -43042,7 +43134,7 @@
         <v>1248838.25838418</v>
       </c>
       <c r="DS116" t="n">
-        <v>1164928.54896317</v>
+        <v>1164928.54896316</v>
       </c>
     </row>
     <row r="117">
@@ -44491,10 +44583,10 @@
         <v>0</v>
       </c>
       <c r="DR120" t="n">
-        <v>1304577.83087437</v>
+        <v>1304577.83087436</v>
       </c>
       <c r="DS120" t="n">
-        <v>1199117.51928923</v>
+        <v>1199117.51928924</v>
       </c>
     </row>
     <row r="121">
@@ -45960,7 +46052,7 @@
         <v>1368040.31112797</v>
       </c>
       <c r="DS124" t="n">
-        <v>1234415.77021774</v>
+        <v>1234415.77021775</v>
       </c>
     </row>
     <row r="125">
@@ -46695,7 +46787,7 @@
         <v>0</v>
       </c>
       <c r="DR126" t="n">
-        <v>1402200.03396728</v>
+        <v>1402200.03396727</v>
       </c>
       <c r="DS126" t="n">
         <v>1253273.93193036</v>
@@ -47069,7 +47161,7 @@
         <v>1419951.99957956</v>
       </c>
       <c r="DS127" t="n">
-        <v>1263282.15294723</v>
+        <v>1263282.15294724</v>
       </c>
     </row>
     <row r="128">
@@ -47437,10 +47529,10 @@
         <v>0</v>
       </c>
       <c r="DR128" t="n">
-        <v>1437928.7065094</v>
+        <v>1437928.70650939</v>
       </c>
       <c r="DS128" t="n">
-        <v>1273370.29622641</v>
+        <v>1273370.29622642</v>
       </c>
     </row>
     <row r="129">
@@ -49666,7 +49758,7 @@
         <v>1542610.20554088</v>
       </c>
       <c r="DS134" t="n">
-        <v>1335494.88118824</v>
+        <v>1335494.88118823</v>
       </c>
     </row>
     <row r="135">
@@ -50034,10 +50126,10 @@
         <v>0</v>
       </c>
       <c r="DR135" t="n">
-        <v>1562892.62595068</v>
+        <v>1562892.62595067</v>
       </c>
       <c r="DS135" t="n">
-        <v>1346599.33293166</v>
+        <v>1346599.33293167</v>
       </c>
     </row>
     <row r="136">
@@ -51892,7 +51984,7 @@
         <v>1657864.17892698</v>
       </c>
       <c r="DS140" t="n">
-        <v>1396855.7917321</v>
+        <v>1396855.79173209</v>
       </c>
     </row>
     <row r="141">
@@ -53005,7 +53097,7 @@
         <v>1710917.43711086</v>
       </c>
       <c r="DS143" t="n">
-        <v>1429886.14236274</v>
+        <v>1429886.14236275</v>
       </c>
     </row>
     <row r="144">
@@ -54115,7 +54207,7 @@
         <v>0</v>
       </c>
       <c r="DR146" t="n">
-        <v>1761782.12991477</v>
+        <v>1761782.12991478</v>
       </c>
       <c r="DS146" t="n">
         <v>1465047.16093972</v>
@@ -55599,7 +55691,7 @@
         <v>0</v>
       </c>
       <c r="DR150" t="n">
-        <v>1822716.37124635</v>
+        <v>1822716.37124634</v>
       </c>
       <c r="DS150" t="n">
         <v>1510533.16517459</v>
@@ -56341,10 +56433,10 @@
         <v>0</v>
       </c>
       <c r="DR152" t="n">
-        <v>1851172.01766877</v>
+        <v>1851172.01766878</v>
       </c>
       <c r="DS152" t="n">
-        <v>1534066.96209426</v>
+        <v>1534066.96209425</v>
       </c>
     </row>
     <row r="153">
@@ -57083,7 +57175,7 @@
         <v>0</v>
       </c>
       <c r="DR154" t="n">
-        <v>1876485.2588576</v>
+        <v>1876485.25885761</v>
       </c>
       <c r="DS154" t="n">
         <v>1555706.15823119</v>
@@ -58938,7 +59030,7 @@
         <v>0</v>
       </c>
       <c r="DR159" t="n">
-        <v>1928747.28837761</v>
+        <v>1928747.28837762</v>
       </c>
       <c r="DS159" t="n">
         <v>1601334.71417783</v>
@@ -60054,7 +60146,7 @@
         <v>1956376.81227447</v>
       </c>
       <c r="DS162" t="n">
-        <v>1625398.9506156</v>
+        <v>1625398.95061561</v>
       </c>
     </row>
     <row r="163">
@@ -60796,7 +60888,7 @@
         <v>1973121.16025245</v>
       </c>
       <c r="DS164" t="n">
-        <v>1641209.26543091</v>
+        <v>1641209.2654309</v>
       </c>
     </row>
     <row r="165">
@@ -61909,7 +62001,7 @@
         <v>1998455.85701136</v>
       </c>
       <c r="DS167" t="n">
-        <v>1663141.3362634</v>
+        <v>1663141.33626339</v>
       </c>
     </row>
     <row r="168">
@@ -64503,10 +64595,10 @@
         <v>0</v>
       </c>
       <c r="DR174" t="n">
-        <v>2064287.06394572</v>
+        <v>2064287.06394571</v>
       </c>
       <c r="DS174" t="n">
-        <v>1730919.56947904</v>
+        <v>1730919.56947905</v>
       </c>
     </row>
     <row r="175">
@@ -64877,7 +64969,7 @@
         <v>2078067.51122046</v>
       </c>
       <c r="DS175" t="n">
-        <v>1742560.91001836</v>
+        <v>1742560.91001835</v>
       </c>
     </row>
     <row r="176">
@@ -66358,7 +66450,7 @@
         <v>0</v>
       </c>
       <c r="DR179" t="n">
-        <v>2136213.39921601</v>
+        <v>2136213.399216</v>
       </c>
       <c r="DS179" t="n">
         <v>1785247.97027612</v>
@@ -68216,7 +68308,7 @@
         <v>2204557.43338134</v>
       </c>
       <c r="DS184" t="n">
-        <v>1832811.13062513</v>
+        <v>1832811.13062512</v>
       </c>
     </row>
     <row r="185">
@@ -68958,7 +69050,7 @@
         <v>2229087.86647003</v>
       </c>
       <c r="DS186" t="n">
-        <v>1853920.90926608</v>
+        <v>1853920.90926609</v>
       </c>
     </row>
     <row r="187">
@@ -69329,7 +69421,7 @@
         <v>2241004.09584186</v>
       </c>
       <c r="DS187" t="n">
-        <v>1865611.0706018</v>
+        <v>1865611.07060181</v>
       </c>
     </row>
     <row r="188">
@@ -69700,7 +69792,7 @@
         <v>2252984.02684007</v>
       </c>
       <c r="DS188" t="n">
-        <v>1877374.94590847</v>
+        <v>1877374.94590848</v>
       </c>
     </row>
     <row r="189">
@@ -70810,10 +70902,10 @@
         <v>6.090567959</v>
       </c>
       <c r="DR191" t="n">
-        <v>2294978.48227385</v>
+        <v>2294978.48227386</v>
       </c>
       <c r="DS191" t="n">
-        <v>1915175.11058963</v>
+        <v>1915175.11058962</v>
       </c>
     </row>
     <row r="192">
@@ -71184,7 +71276,7 @@
         <v>2310101.91101896</v>
       </c>
       <c r="DS192" t="n">
-        <v>1928289.65307578</v>
+        <v>1928289.65307577</v>
       </c>
     </row>
     <row r="193">
@@ -71926,7 +72018,7 @@
         <v>2342389.97588629</v>
       </c>
       <c r="DS194" t="n">
-        <v>1953715.12254476</v>
+        <v>1953715.12254477</v>
       </c>
     </row>
     <row r="195">
@@ -72665,7 +72757,7 @@
         <v>3.229812508</v>
       </c>
       <c r="DR196" t="n">
-        <v>2376896.55344149</v>
+        <v>2376896.55344148</v>
       </c>
       <c r="DS196" t="n">
         <v>1978388.6367801</v>
@@ -73039,7 +73131,7 @@
         <v>2394340</v>
       </c>
       <c r="DS197" t="n">
-        <v>1990842</v>
+        <v>1990842.00000001</v>
       </c>
     </row>
     <row r="198">
@@ -73407,7 +73499,7 @@
         <v>2.63238919</v>
       </c>
       <c r="DR198" t="n">
-        <v>2414890.65301887</v>
+        <v>2414890.65301886</v>
       </c>
       <c r="DS198" t="n">
         <v>2001935.67818076</v>
@@ -73778,7 +73870,7 @@
         <v>2.251559539</v>
       </c>
       <c r="DR199" t="n">
-        <v>2435617.6925741</v>
+        <v>2435617.69257411</v>
       </c>
       <c r="DS199" t="n">
         <v>2013091.17427354</v>
@@ -74149,7 +74241,7 @@
         <v>2.522693496</v>
       </c>
       <c r="DR200" t="n">
-        <v>2456522.63259377</v>
+        <v>2456522.63259378</v>
       </c>
       <c r="DS200" t="n">
         <v>2024308.83274966</v>
@@ -75265,7 +75357,7 @@
         <v>2518455.26762716</v>
       </c>
       <c r="DS203" t="n">
-        <v>2056312.51114294</v>
+        <v>2056312.51114295</v>
       </c>
     </row>
     <row r="204">
@@ -75468,11 +75560,21 @@
       <c r="BO204" t="n">
         <v>2310.9387459</v>
       </c>
-      <c r="BP204"/>
-      <c r="BQ204"/>
-      <c r="BR204"/>
-      <c r="BS204"/>
-      <c r="BT204"/>
+      <c r="BP204" t="n">
+        <v>1208.3</v>
+      </c>
+      <c r="BQ204" t="n">
+        <v>296.284</v>
+      </c>
+      <c r="BR204" t="n">
+        <v>46071</v>
+      </c>
+      <c r="BS204" t="n">
+        <v>78074</v>
+      </c>
+      <c r="BT204" t="n">
+        <v>39206</v>
+      </c>
       <c r="BU204" t="n">
         <v>14503.3755150333</v>
       </c>
@@ -75531,11 +75633,21 @@
       <c r="DD204"/>
       <c r="DE204"/>
       <c r="DF204"/>
-      <c r="DG204"/>
-      <c r="DH204"/>
-      <c r="DI204"/>
-      <c r="DJ204"/>
-      <c r="DK204"/>
+      <c r="DG204" t="n">
+        <v>3858.589</v>
+      </c>
+      <c r="DH204" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DI204" t="n">
+        <v>0.06414872</v>
+      </c>
+      <c r="DJ204" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK204" t="n">
+        <v>8126.89990234375</v>
+      </c>
       <c r="DL204"/>
       <c r="DM204"/>
       <c r="DN204" t="n">
@@ -75544,8 +75656,12 @@
       <c r="DO204"/>
       <c r="DP204"/>
       <c r="DQ204"/>
-      <c r="DR204"/>
-      <c r="DS204"/>
+      <c r="DR204" t="n">
+        <v>2538962.89764061</v>
+      </c>
+      <c r="DS204" t="n">
+        <v>2066700.50553437</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n">
@@ -75747,11 +75863,21 @@
       <c r="BO205" t="n">
         <v>2385.7573131</v>
       </c>
-      <c r="BP205"/>
-      <c r="BQ205"/>
-      <c r="BR205"/>
-      <c r="BS205"/>
-      <c r="BT205"/>
+      <c r="BP205" t="n">
+        <v>1222.865</v>
+      </c>
+      <c r="BQ205" t="n">
+        <v>296.313</v>
+      </c>
+      <c r="BR205" t="n">
+        <v>46834</v>
+      </c>
+      <c r="BS205" t="n">
+        <v>78630</v>
+      </c>
+      <c r="BT205" t="n">
+        <v>38314</v>
+      </c>
       <c r="BU205" t="n">
         <v>14589.9722275667</v>
       </c>
@@ -75810,11 +75936,21 @@
       <c r="DD205"/>
       <c r="DE205"/>
       <c r="DF205"/>
-      <c r="DG205"/>
-      <c r="DH205"/>
-      <c r="DI205"/>
-      <c r="DJ205"/>
-      <c r="DK205"/>
+      <c r="DG205" t="n">
+        <v>3994.233</v>
+      </c>
+      <c r="DH205" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DI205" t="n">
+        <v>0.06414872</v>
+      </c>
+      <c r="DJ205" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK205" t="n">
+        <v>8773</v>
+      </c>
       <c r="DL205"/>
       <c r="DM205"/>
       <c r="DN205" t="n">
@@ -75823,8 +75959,12 @@
       <c r="DO205"/>
       <c r="DP205"/>
       <c r="DQ205"/>
-      <c r="DR205"/>
-      <c r="DS205"/>
+      <c r="DR205" t="n">
+        <v>2559470.52765406</v>
+      </c>
+      <c r="DS205" t="n">
+        <v>2077088.49992579</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n">
@@ -76026,11 +76166,21 @@
       <c r="BO206" t="n">
         <v>2357.3096456</v>
       </c>
-      <c r="BP206"/>
-      <c r="BQ206"/>
-      <c r="BR206"/>
-      <c r="BS206"/>
-      <c r="BT206"/>
+      <c r="BP206" t="n">
+        <v>1250.722</v>
+      </c>
+      <c r="BQ206" t="n">
+        <v>294.716</v>
+      </c>
+      <c r="BR206" t="n">
+        <v>47672</v>
+      </c>
+      <c r="BS206" t="n">
+        <v>79181</v>
+      </c>
+      <c r="BT206" t="n">
+        <v>37427</v>
+      </c>
       <c r="BU206" t="n">
         <v>14608.7589597667</v>
       </c>
@@ -76089,11 +76239,21 @@
       <c r="DD206"/>
       <c r="DE206"/>
       <c r="DF206"/>
-      <c r="DG206"/>
-      <c r="DH206"/>
-      <c r="DI206"/>
-      <c r="DJ206"/>
-      <c r="DK206"/>
+      <c r="DG206" t="n">
+        <v>4169.342</v>
+      </c>
+      <c r="DH206" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DI206" t="n">
+        <v>0.06414872</v>
+      </c>
+      <c r="DJ206" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK206" t="n">
+        <v>9135.900390625</v>
+      </c>
       <c r="DL206"/>
       <c r="DM206"/>
       <c r="DN206" t="n">
@@ -76102,8 +76262,12 @@
       <c r="DO206"/>
       <c r="DP206"/>
       <c r="DQ206"/>
-      <c r="DR206"/>
-      <c r="DS206"/>
+      <c r="DR206" t="n">
+        <v>2579978.15766751</v>
+      </c>
+      <c r="DS206" t="n">
+        <v>2087476.49431721</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n">
@@ -76303,11 +76467,21 @@
       <c r="BO207" t="n">
         <v>2363.9815529</v>
       </c>
-      <c r="BP207"/>
-      <c r="BQ207"/>
-      <c r="BR207"/>
-      <c r="BS207"/>
-      <c r="BT207"/>
+      <c r="BP207" t="n">
+        <v>1274.866</v>
+      </c>
+      <c r="BQ207" t="n">
+        <v>294.664</v>
+      </c>
+      <c r="BR207" t="n">
+        <v>48231</v>
+      </c>
+      <c r="BS207" t="n">
+        <v>80448</v>
+      </c>
+      <c r="BT207" t="n">
+        <v>37406</v>
+      </c>
       <c r="BU207" t="n">
         <v>14636.2891356667</v>
       </c>
@@ -76364,11 +76538,21 @@
       <c r="DD207"/>
       <c r="DE207"/>
       <c r="DF207"/>
-      <c r="DG207"/>
-      <c r="DH207"/>
-      <c r="DI207"/>
-      <c r="DJ207"/>
-      <c r="DK207"/>
+      <c r="DG207" t="n">
+        <v>4202.017</v>
+      </c>
+      <c r="DH207" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DI207" t="n">
+        <v>0.06414872</v>
+      </c>
+      <c r="DJ207" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK207" t="n">
+        <v>9018.7998046875</v>
+      </c>
       <c r="DL207"/>
       <c r="DM207"/>
       <c r="DN207" t="n">
@@ -76377,8 +76561,12 @@
       <c r="DO207"/>
       <c r="DP207"/>
       <c r="DQ207"/>
-      <c r="DR207"/>
-      <c r="DS207"/>
+      <c r="DR207" t="n">
+        <v>2600485.78768096</v>
+      </c>
+      <c r="DS207" t="n">
+        <v>2097864.48870863</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n">
@@ -76572,9 +76760,15 @@
       <c r="BO208"/>
       <c r="BP208"/>
       <c r="BQ208"/>
-      <c r="BR208"/>
-      <c r="BS208"/>
-      <c r="BT208"/>
+      <c r="BR208" t="n">
+        <v>48366</v>
+      </c>
+      <c r="BS208" t="n">
+        <v>82084</v>
+      </c>
+      <c r="BT208" t="n">
+        <v>37980</v>
+      </c>
       <c r="BU208" t="n">
         <v>14718.9240242333</v>
       </c>
@@ -76622,10 +76816,18 @@
       <c r="DE208"/>
       <c r="DF208"/>
       <c r="DG208"/>
-      <c r="DH208"/>
-      <c r="DI208"/>
-      <c r="DJ208"/>
-      <c r="DK208"/>
+      <c r="DH208" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DI208" t="n">
+        <v>0.06414872</v>
+      </c>
+      <c r="DJ208" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK208" t="n">
+        <v>8885.599609375</v>
+      </c>
       <c r="DL208"/>
       <c r="DM208"/>
       <c r="DN208" t="n">
@@ -76634,8 +76836,12 @@
       <c r="DO208"/>
       <c r="DP208"/>
       <c r="DQ208"/>
-      <c r="DR208"/>
-      <c r="DS208"/>
+      <c r="DR208" t="n">
+        <v>2620993.41769441</v>
+      </c>
+      <c r="DS208" t="n">
+        <v>2108252.48310005</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n">
@@ -76781,18 +76987,30 @@
       <c r="DE209"/>
       <c r="DF209"/>
       <c r="DG209"/>
-      <c r="DH209"/>
-      <c r="DI209"/>
-      <c r="DJ209"/>
-      <c r="DK209"/>
+      <c r="DH209" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DI209" t="n">
+        <v>0.06414872</v>
+      </c>
+      <c r="DJ209" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK209" t="n">
+        <v>8986.2001953125</v>
+      </c>
       <c r="DL209"/>
       <c r="DM209"/>
       <c r="DN209"/>
       <c r="DO209"/>
       <c r="DP209"/>
       <c r="DQ209"/>
-      <c r="DR209"/>
-      <c r="DS209"/>
+      <c r="DR209" t="n">
+        <v>2641501.04770786</v>
+      </c>
+      <c r="DS209" t="n">
+        <v>2118640.47749147</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n">
@@ -76928,18 +77146,30 @@
       <c r="DE210"/>
       <c r="DF210"/>
       <c r="DG210"/>
-      <c r="DH210"/>
-      <c r="DI210"/>
-      <c r="DJ210"/>
-      <c r="DK210"/>
+      <c r="DH210" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DI210" t="n">
+        <v>0.06414872</v>
+      </c>
+      <c r="DJ210" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK210" t="n">
+        <v>9156.400390625</v>
+      </c>
       <c r="DL210"/>
       <c r="DM210"/>
       <c r="DN210"/>
       <c r="DO210"/>
       <c r="DP210"/>
       <c r="DQ210"/>
-      <c r="DR210"/>
-      <c r="DS210"/>
+      <c r="DR210" t="n">
+        <v>2662008.67772131</v>
+      </c>
+      <c r="DS210" t="n">
+        <v>2129028.47188289</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-raw/Data.xlsx
+++ b/data-raw/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="8" state="visible" r:id="rId3"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="634">
   <si>
     <t>date</t>
   </si>
@@ -1907,6 +1907,21 @@
   <si>
     <t xml:space="preserve">Public-sector net debt from annual fiscal data (ABS GFS annual net debt checked: 846.6b 2023-24, 954.9b 2024-25; the workbook's quarterly path is a custom interpolation - the derivation is needed)</t>
   </si>
+  <si>
+    <t xml:space="preserve">Derived: Peq / PeRatio (validated 0.000% over 82 quarters; the model's EqYield identity). PeRatio upstream is the LSEG/Refinitiv ASX calculated P/E - free endpoints tested (ASX archive: index/market-cap only; marketindex.com.au: Cloudflare; RBA: discontinued 2011; Yahoo/FRED: no P/E)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom quarterly interpolation of the annual fiscal balance (structure identified: annual sums match general-government net lending, e.g. 2022: ~80.6b, 2023: ~28.2b, 2024: ~45.8b; GFS quarterly checked and differs - the owner's interpolation kernel and annual vintage are needed to extend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linear interpolation between June-quarter annual net debt levels (structure validated exactly: +26.9/quarter Jun-2023 to Jun-2024 = 661.7 to 769.3; current GFS annual net debt 783.8/846.6/954.9 does not match the workbook's vintage - the owner's annual source is needed to extend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AEM PCPIUX internal splice (CPI excluding GST effects) - not reproducible from published ABS series (ratio to Pcpi drifts 0.0095-0.0102); the splice is the source record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy EViews SEM NAIRU estimate via Masterdata - unused by the model (superseded by LurHpf per the variable audit); kept for history</t>
+  </si>
 </sst>
 </file>
 
@@ -3565,7 +3580,7 @@
         <v>218</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>71</v>
@@ -3747,7 +3762,7 @@
         <v>460</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>244</v>
@@ -3761,7 +3776,7 @@
         <v>462</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>220</v>
@@ -3869,7 +3884,7 @@
         <v>233</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>234</v>
+        <v>633</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>329</v>
@@ -3911,7 +3926,7 @@
         <v>241</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>242</v>
+        <v>632</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>243</v>
@@ -45970,7 +45985,7 @@
         <v>16.2143333333333</v>
       </c>
       <c r="CQ124" t="n">
-        <v>252.899697798244</v>
+        <v>252.899697798245</v>
       </c>
       <c r="CR124" t="n">
         <v>47.1</v>
@@ -47448,7 +47463,7 @@
         <v>15.8187301587302</v>
       </c>
       <c r="CQ128" t="n">
-        <v>321.593449597624</v>
+        <v>321.593449597623</v>
       </c>
       <c r="CR128" t="n">
         <v>53.2</v>
@@ -47819,7 +47834,7 @@
         <v>14.8493442622951</v>
       </c>
       <c r="CQ129" t="n">
-        <v>339.004868570672</v>
+        <v>339.004868570671</v>
       </c>
       <c r="CR129" t="n">
         <v>21.4</v>
@@ -48561,7 +48576,7 @@
         <v>15.4328571428571</v>
       </c>
       <c r="CQ131" t="n">
-        <v>365.7326668518</v>
+        <v>365.732666851801</v>
       </c>
       <c r="CR131" t="n">
         <v>50.6</v>
@@ -48932,7 +48947,7 @@
         <v>14.8138095238095</v>
       </c>
       <c r="CQ132" t="n">
-        <v>403.596386897682</v>
+        <v>403.596386897683</v>
       </c>
       <c r="CR132" t="n">
         <v>76</v>
@@ -49303,7 +49318,7 @@
         <v>15.1886885245902</v>
       </c>
       <c r="CQ133" t="n">
-        <v>415.480243062676</v>
+        <v>415.480243062675</v>
       </c>
       <c r="CR133" t="n">
         <v>49.2</v>
@@ -50787,7 +50802,7 @@
         <v>13.3449206349206</v>
       </c>
       <c r="CQ137" t="n">
-        <v>399.620211007101</v>
+        <v>399.620211007102</v>
       </c>
       <c r="CR137" t="n">
         <v>65.1</v>
@@ -51158,7 +51173,7 @@
         <v>12.3561538461539</v>
       </c>
       <c r="CQ138" t="n">
-        <v>374.817281952313</v>
+        <v>374.817281952311</v>
       </c>
       <c r="CR138" t="n">
         <v>84.1</v>
@@ -52642,7 +52657,7 @@
         <v>11.6742424242424</v>
       </c>
       <c r="CQ142" t="n">
-        <v>405.962102530824</v>
+        <v>405.962102530825</v>
       </c>
       <c r="CR142" t="n">
         <v>62.5</v>
@@ -53755,7 +53770,7 @@
         <v>16.8435849056604</v>
       </c>
       <c r="CQ145" t="n">
-        <v>256.762442450516</v>
+        <v>256.762442450515</v>
       </c>
       <c r="CR145" t="n">
         <v>32</v>
@@ -54868,7 +54883,7 @@
         <v>15.3264516129032</v>
       </c>
       <c r="CQ148" t="n">
-        <v>321.574760060616</v>
+        <v>321.574760060617</v>
       </c>
       <c r="CR148" t="n">
         <v>61</v>
@@ -56352,7 +56367,7 @@
         <v>12.3142857142857</v>
       </c>
       <c r="CQ152" t="n">
-        <v>358.932714617169</v>
+        <v>358.93271461717</v>
       </c>
       <c r="CR152" t="n">
         <v>74</v>
@@ -56723,7 +56738,7 @@
         <v>12.4459016393443</v>
       </c>
       <c r="CQ153" t="n">
-        <v>332.278055848261</v>
+        <v>332.27805584826</v>
       </c>
       <c r="CR153" t="n">
         <v>51.9</v>
@@ -58578,7 +58593,7 @@
         <v>16.6713636363636</v>
       </c>
       <c r="CQ158" t="n">
-        <v>312.973798293208</v>
+        <v>312.973798293209</v>
       </c>
       <c r="CR158" t="n">
         <v>54.2</v>
@@ -59320,7 +59335,7 @@
         <v>16.086935483871</v>
       </c>
       <c r="CQ160" t="n">
-        <v>335.862601389627</v>
+        <v>335.862601389626</v>
       </c>
       <c r="CR160" t="n">
         <v>65</v>
@@ -59691,7 +59706,7 @@
         <v>15.7631147540984</v>
       </c>
       <c r="CQ161" t="n">
-        <v>341.429982840206</v>
+        <v>341.429982840205</v>
       </c>
       <c r="CR161" t="n">
         <v>30.4</v>
@@ -60804,7 +60819,7 @@
         <v>14.3554838709677</v>
       </c>
       <c r="CQ164" t="n">
-        <v>408.338726349378</v>
+        <v>408.338726349379</v>
       </c>
       <c r="CR164" t="n">
         <v>63.8</v>
@@ -61175,7 +61190,7 @@
         <v>14.5253225806452</v>
       </c>
       <c r="CQ165" t="n">
-        <v>375.289427806833</v>
+        <v>375.289427806832</v>
       </c>
       <c r="CR165" t="n">
         <v>33.3</v>
@@ -61546,7 +61561,7 @@
         <v>14.4622727272727</v>
       </c>
       <c r="CQ166" t="n">
-        <v>349.779048936103</v>
+        <v>349.779048936104</v>
       </c>
       <c r="CR166" t="n">
         <v>50.4</v>
@@ -62288,7 +62303,7 @@
         <v>14.7988333333333</v>
       </c>
       <c r="CQ168" t="n">
-        <v>348.122036647033</v>
+        <v>348.122036647034</v>
       </c>
       <c r="CR168" t="n">
         <v>73</v>
@@ -62659,7 +62674,7 @@
         <v>15.7544444444445</v>
       </c>
       <c r="CQ169" t="n">
-        <v>337.073136328373</v>
+        <v>337.073136328372</v>
       </c>
       <c r="CR169" t="n">
         <v>43.6</v>
@@ -63030,7 +63045,7 @@
         <v>16.7315151515152</v>
       </c>
       <c r="CQ170" t="n">
-        <v>330.227116311081</v>
+        <v>330.22711631108</v>
       </c>
       <c r="CR170" t="n">
         <v>73.7</v>
@@ -63772,7 +63787,7 @@
         <v>17.9634920634921</v>
       </c>
       <c r="CQ172" t="n">
-        <v>328.655474065565</v>
+        <v>328.655474065564</v>
       </c>
       <c r="CR172" t="n">
         <v>88.8</v>
@@ -64143,7 +64158,7 @@
         <v>17.6606557377049</v>
       </c>
       <c r="CQ173" t="n">
-        <v>326.37519725239</v>
+        <v>326.375197252391</v>
       </c>
       <c r="CR173" t="n">
         <v>47.3</v>
@@ -64514,7 +64529,7 @@
         <v>16.3112307692308</v>
       </c>
       <c r="CQ174" t="n">
-        <v>352.205181894495</v>
+        <v>352.205181894494</v>
       </c>
       <c r="CR174" t="n">
         <v>69.7</v>
@@ -65256,7 +65271,7 @@
         <v>15.7241935483871</v>
       </c>
       <c r="CQ176" t="n">
-        <v>373.240127192533</v>
+        <v>373.240127192532</v>
       </c>
       <c r="CR176" t="n">
         <v>85.1</v>
@@ -65627,7 +65642,7 @@
         <v>15.8003225806452</v>
       </c>
       <c r="CQ177" t="n">
-        <v>398.074151201486</v>
+        <v>398.074151201485</v>
       </c>
       <c r="CR177" t="n">
         <v>47.6</v>
@@ -66740,7 +66755,7 @@
         <v>12.6023728813559</v>
       </c>
       <c r="CQ180" t="n">
-        <v>496.866745568497</v>
+        <v>496.866745568498</v>
       </c>
       <c r="CR180" t="n">
         <v>83.6</v>
@@ -67111,7 +67126,7 @@
         <v>14.3034426229508</v>
       </c>
       <c r="CQ181" t="n">
-        <v>468.362769481152</v>
+        <v>468.362769481153</v>
       </c>
       <c r="CR181" t="n">
         <v>38.2</v>
@@ -68595,7 +68610,7 @@
         <v>15.1154838709677</v>
       </c>
       <c r="CQ185" t="n">
-        <v>397.029962866533</v>
+        <v>397.029962866534</v>
       </c>
       <c r="CR185" t="n">
         <v>-8.3</v>
@@ -69708,7 +69723,7 @@
         <v>21.4329508196721</v>
       </c>
       <c r="CQ188" t="n">
-        <v>327.393090155345</v>
+        <v>327.393090155346</v>
       </c>
       <c r="CR188" t="n">
         <v>-14.2</v>
@@ -70079,7 +70094,7 @@
         <v>21.3114516129032</v>
       </c>
       <c r="CQ189" t="n">
-        <v>355.911935881814</v>
+        <v>355.911935881815</v>
       </c>
       <c r="CR189" t="n">
         <v>1.1</v>
@@ -71192,7 +71207,7 @@
         <v>13.8409836065574</v>
       </c>
       <c r="CQ192" t="n">
-        <v>562.792372379486</v>
+        <v>562.792372379485</v>
       </c>
       <c r="CR192" t="n">
         <v>107.5</v>
@@ -71563,7 +71578,7 @@
         <v>10.9762295081967</v>
       </c>
       <c r="CQ193" t="n">
-        <v>614.646404301396</v>
+        <v>614.646404301398</v>
       </c>
       <c r="CR193" t="n">
         <v>78</v>
@@ -71934,7 +71949,7 @@
         <v>10.3707692307692</v>
       </c>
       <c r="CQ194" t="n">
-        <v>643.992731048806</v>
+        <v>643.992731048808</v>
       </c>
       <c r="CR194" t="n">
         <v>127.7</v>
@@ -72305,7 +72320,7 @@
         <v>10.7598387096774</v>
       </c>
       <c r="CQ195" t="n">
-        <v>671.171770772436</v>
+        <v>671.171770772438</v>
       </c>
       <c r="CR195" t="n">
         <v>124.6</v>
@@ -72676,7 +72691,7 @@
         <v>11.4987301587302</v>
       </c>
       <c r="CQ196" t="n">
-        <v>641.227326688937</v>
+        <v>641.227326688935</v>
       </c>
       <c r="CR196" t="n">
         <v>165.5</v>
@@ -73047,7 +73062,7 @@
         <v>11.3130508474576</v>
       </c>
       <c r="CQ197" t="n">
-        <v>654.244385515454</v>
+        <v>654.244385515456</v>
       </c>
       <c r="CR197" t="n">
         <v>120.5</v>
@@ -74160,7 +74175,7 @@
         <v>17.2203333333333</v>
       </c>
       <c r="CQ200" t="n">
-        <v>473.492576605176</v>
+        <v>473.492576605177</v>
       </c>
       <c r="CR200" t="n">
         <v>128.7</v>
@@ -74531,7 +74546,7 @@
         <v>20.1301639344262</v>
       </c>
       <c r="CQ201" t="n">
-        <v>398.09909278955</v>
+        <v>398.099092789551</v>
       </c>
       <c r="CR201" t="n">
         <v>55.8</v>
@@ -74902,7 +74917,7 @@
         <v>19.0115151515152</v>
       </c>
       <c r="CQ202" t="n">
-        <v>440.801268768529</v>
+        <v>440.801268768528</v>
       </c>
       <c r="CR202" t="n">
         <v>81.6</v>
@@ -75273,7 +75288,7 @@
         <v>17.4153333333333</v>
       </c>
       <c r="CQ203" t="n">
-        <v>503.209510846212</v>
+        <v>503.209510846213</v>
       </c>
       <c r="CR203" t="n">
         <v>64.3</v>
